--- a/Clean/Data_Preprocessing_Specification.xlsx
+++ b/Clean/Data_Preprocessing_Specification.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Downloads/Thai/Graduation_Thesis/Clean/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Documents/GitHub/Graduation_Thesis/Clean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B282AB1-FDE8-B640-8A8A-D1B09F55557B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1637CF22-FBF5-F248-B1DD-95318ABBE42D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16080" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1_Raw_Data_Fields" sheetId="1" r:id="rId1"/>
@@ -124,9 +124,6 @@
     <t xml:space="preserve">DANH MỤC CÁC TRƯỜNG DỮ LIỆU THÔ </t>
   </si>
   <si>
-    <t xml:space="preserve">Nguồn: batdongsan.com.vn | Tập thô: 30,335 dòng × 23 cột </t>
-  </si>
-  <si>
     <t>Tên trường (Field Name)</t>
   </si>
   <si>
@@ -1141,6 +1138,9 @@
   </si>
   <si>
     <t>Ý nghĩa &amp; Tác động học máy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguồn: batdongsan.com.vn | Tập thô: 31,292 dòng × 23 cột </t>
   </si>
 </sst>
 </file>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="2" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
-        <v>33</v>
+        <v>321</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -1754,16 +1754,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
@@ -1771,16 +1771,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="D4" s="4">
         <v>46279811</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="35" customHeight="1" x14ac:dyDescent="0.2">
@@ -1788,16 +1788,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
@@ -1805,16 +1805,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
@@ -1822,16 +1822,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="37" customHeight="1" x14ac:dyDescent="0.2">
@@ -1839,16 +1839,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
@@ -1856,16 +1856,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
@@ -1873,16 +1873,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -1890,16 +1890,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="D11" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>67</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="43" customHeight="1" x14ac:dyDescent="0.2">
@@ -1907,16 +1907,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="52" customHeight="1" x14ac:dyDescent="0.2">
@@ -1924,16 +1924,16 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="D13" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.2">
@@ -1941,16 +1941,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -1958,16 +1958,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="E15" s="7" t="s">
         <v>83</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
@@ -1975,16 +1975,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -1992,16 +1992,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="D17" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="E17" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -2009,16 +2009,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="44" customHeight="1" x14ac:dyDescent="0.2">
@@ -2026,16 +2026,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="D19" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
@@ -2043,16 +2043,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="E20" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="56" customHeight="1" x14ac:dyDescent="0.2">
@@ -2060,16 +2060,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.2">
@@ -2077,16 +2077,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
@@ -2094,16 +2094,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="D23" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="49" customHeight="1" x14ac:dyDescent="0.2">
@@ -2111,16 +2111,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="41" customHeight="1" x14ac:dyDescent="0.2">
@@ -2128,16 +2128,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="D25" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.2">
@@ -2145,16 +2145,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2181,7 +2181,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -2194,19 +2194,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>133</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="193" customHeight="1" x14ac:dyDescent="0.2">
@@ -2214,19 +2214,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="E3" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>138</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="113" customHeight="1" x14ac:dyDescent="0.2">
@@ -2234,19 +2234,19 @@
         <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="D4" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>143</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="153" customHeight="1" x14ac:dyDescent="0.2">
@@ -2254,19 +2254,19 @@
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="E5" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="F5" s="10" t="s">
         <v>148</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="187" customHeight="1" x14ac:dyDescent="0.2">
@@ -2274,19 +2274,19 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="F6" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -2294,19 +2294,19 @@
         <v>5</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="F7" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="119" customHeight="1" x14ac:dyDescent="0.2">
@@ -2314,19 +2314,19 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>163</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -2334,19 +2334,19 @@
         <v>7</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>168</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="204" customHeight="1" x14ac:dyDescent="0.2">
@@ -2354,19 +2354,19 @@
         <v>8</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="E10" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="F10" s="12" t="s">
         <v>173</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="170" customHeight="1" x14ac:dyDescent="0.2">
@@ -2374,19 +2374,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="F11" s="10" t="s">
         <v>178</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="136" customHeight="1" x14ac:dyDescent="0.2">
@@ -2394,19 +2394,19 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="D12" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="E12" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="F12" s="12" t="s">
         <v>183</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -2414,19 +2414,19 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="F13" s="10" t="s">
         <v>188</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="204" customHeight="1" x14ac:dyDescent="0.2">
@@ -2434,19 +2434,19 @@
         <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C14" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="D14" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="E14" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="F14" s="12" t="s">
         <v>193</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="119" customHeight="1" x14ac:dyDescent="0.2">
@@ -2454,19 +2454,19 @@
         <v>13</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="F15" s="10" t="s">
         <v>198</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
@@ -2474,19 +2474,19 @@
         <v>14</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="F16" s="12" t="s">
         <v>203</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="68" customHeight="1" x14ac:dyDescent="0.2">
@@ -2494,19 +2494,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="D17" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="10" t="s">
         <v>208</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="85" customHeight="1" x14ac:dyDescent="0.2">
@@ -2514,19 +2514,19 @@
         <v>16</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="D18" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="E18" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="F18" s="12" t="s">
         <v>213</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="360" customHeight="1" x14ac:dyDescent="0.2">
@@ -2534,19 +2534,19 @@
         <v>17</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="D19" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="E19" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="F19" s="10" t="s">
         <v>218</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="119" customHeight="1" x14ac:dyDescent="0.2">
@@ -2554,19 +2554,19 @@
         <v>18</v>
       </c>
       <c r="B20" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="D20" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="E20" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="F20" s="12" t="s">
         <v>223</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="170" customHeight="1" x14ac:dyDescent="0.2">
@@ -2574,19 +2574,19 @@
         <v>19</v>
       </c>
       <c r="B21" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="D21" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="F21" s="10" t="s">
         <v>228</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2615,7 +2615,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="33" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -2638,19 +2638,19 @@
         <v>1</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>235</v>
-      </c>
       <c r="F3" s="15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="46" customHeight="1" x14ac:dyDescent="0.2">
@@ -2658,17 +2658,17 @@
         <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>236</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>237</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="47" customHeight="1" x14ac:dyDescent="0.2">
@@ -2676,19 +2676,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>241</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="56" customHeight="1" x14ac:dyDescent="0.2">
@@ -2696,19 +2696,19 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>244</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -2716,17 +2716,17 @@
         <v>4</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>246</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>247</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="47" customHeight="1" x14ac:dyDescent="0.2">
@@ -2734,17 +2734,17 @@
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="53" customHeight="1" x14ac:dyDescent="0.2">
@@ -2752,17 +2752,17 @@
         <v>6</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -2770,17 +2770,17 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2">
@@ -2788,17 +2788,17 @@
         <v>8</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E11" s="7"/>
       <c r="F11" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="37" customHeight="1" x14ac:dyDescent="0.2">
@@ -2806,17 +2806,17 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="46" customHeight="1" x14ac:dyDescent="0.2">
@@ -2824,17 +2824,17 @@
         <v>10</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -2842,17 +2842,17 @@
         <v>11</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="44" customHeight="1" x14ac:dyDescent="0.2">
@@ -2860,17 +2860,17 @@
         <v>12</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C15" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D15" s="17" t="s">
         <v>239</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>240</v>
       </c>
       <c r="E15" s="7"/>
       <c r="F15" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -2878,19 +2878,19 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C16" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.2">
@@ -2898,19 +2898,19 @@
         <v>14</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>239</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="E17" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>263</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -2918,19 +2918,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C18" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="D18" s="16" t="s">
-        <v>240</v>
-      </c>
       <c r="E18" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -2938,19 +2938,19 @@
         <v>16</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C19" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D19" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>240</v>
-      </c>
       <c r="E19" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>267</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -2958,19 +2958,19 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C20" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="D20" s="16" t="s">
-        <v>240</v>
-      </c>
       <c r="E20" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
@@ -2978,19 +2978,19 @@
         <v>18</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C21" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>240</v>
-      </c>
       <c r="E21" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="37" customHeight="1" x14ac:dyDescent="0.2">
@@ -2998,19 +2998,19 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="4" t="s">
         <v>273</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -3018,19 +3018,19 @@
         <v>20</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="C23" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>252</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="7" t="s">
         <v>276</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -3038,19 +3038,19 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D24" s="16" t="s">
+      <c r="E24" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="43" customHeight="1" x14ac:dyDescent="0.2">
@@ -3058,19 +3058,19 @@
         <v>22</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>282</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -3078,19 +3078,19 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>284</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="43" customHeight="1" x14ac:dyDescent="0.2">
@@ -3098,19 +3098,19 @@
         <v>24</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="C27" s="17" t="s">
+        <v>238</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>286</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.2">
@@ -3118,19 +3118,19 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="41" customHeight="1" x14ac:dyDescent="0.2">
@@ -3138,19 +3138,19 @@
         <v>26</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="C29" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C29" s="17" t="s">
+      <c r="D29" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="E29" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="F29" s="7" t="s">
         <v>293</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
@@ -3158,19 +3158,19 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="F30" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.2">
@@ -3178,19 +3178,19 @@
         <v>28</v>
       </c>
       <c r="B31" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C31" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
         <v>299</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="117" customHeight="1" x14ac:dyDescent="0.2">
@@ -3198,19 +3198,19 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="C32" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -3218,19 +3218,19 @@
         <v>30</v>
       </c>
       <c r="B33" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="C33" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="D33" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="D33" s="25" t="s">
+      <c r="E33" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="F33" s="10" t="s">
         <v>307</v>
-      </c>
-      <c r="F33" s="10" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -3238,19 +3238,19 @@
         <v>31</v>
       </c>
       <c r="B34" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F34" s="10" t="s">
         <v>309</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="D34" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="F34" s="10" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -3258,19 +3258,19 @@
         <v>32</v>
       </c>
       <c r="B35" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F35" s="10" t="s">
         <v>311</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="D35" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="F35" s="10" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -3278,19 +3278,19 @@
         <v>33</v>
       </c>
       <c r="B36" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>313</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="E36" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="F36" s="10" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -3298,19 +3298,19 @@
         <v>34</v>
       </c>
       <c r="B37" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F37" s="10" t="s">
         <v>315</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="D37" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="E37" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="F37" s="10" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -3318,39 +3318,39 @@
         <v>35</v>
       </c>
       <c r="B38" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F38" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="C38" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="D38" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="E38" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A39" s="23">
         <v>36</v>
       </c>
       <c r="B39" s="24" t="s">
+        <v>318</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="F39" s="10" t="s">
         <v>319</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="D39" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>320</v>
       </c>
     </row>
   </sheetData>
